--- a/data/trans_bre/POLIPATOLOGIA_2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_2-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,13; 20,33</t>
+          <t>12,46; 20,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,59; 19,01</t>
+          <t>10,17; 19,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,78; 23,8</t>
+          <t>14,74; 24,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,5; 21,24</t>
+          <t>11,39; 21,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,35; 55,65</t>
+          <t>30,04; 55,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,25; 40,88</t>
+          <t>20,07; 41,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,36; 57,49</t>
+          <t>31,6; 58,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,78; 41,08</t>
+          <t>19,35; 40,42</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 11,39</t>
+          <t>6,17; 11,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,49; 11,81</t>
+          <t>6,61; 12,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 11,62</t>
+          <t>6,42; 11,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,71; 36,6</t>
+          <t>12,61; 36,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>55,54; 114,86</t>
+          <t>51,79; 115,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,1; 83,08</t>
+          <t>38,43; 84,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,83; 69,48</t>
+          <t>33,05; 70,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>45,14; 176,04</t>
+          <t>44,65; 171,56</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 11,78</t>
+          <t>2,91; 12,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 14,03</t>
+          <t>4,21; 14,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 6,36</t>
+          <t>-3,37; 7,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,25; 15,01</t>
+          <t>5,34; 14,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,72; 131,38</t>
+          <t>18,85; 127,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,73; 159,44</t>
+          <t>27,8; 162,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 40,03</t>
+          <t>-16,87; 48,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17,08; 60,35</t>
+          <t>18,12; 61,67</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,66; 15,95</t>
+          <t>11,6; 15,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,07; 16,5</t>
+          <t>12,02; 16,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,2; 14,48</t>
+          <t>10,1; 14,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,65; 30,36</t>
+          <t>13,81; 29,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,65; 84,85</t>
+          <t>55,88; 83,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,22; 70,76</t>
+          <t>46,73; 71,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,96; 63,73</t>
+          <t>40,75; 65,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>44,49; 116,99</t>
+          <t>43,07; 116,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_2-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,56</t>
+          <t>19,01</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>35,99%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,46; 20,41</t>
+          <t>12,6; 20,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,17; 19,06</t>
+          <t>10,63; 18,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,74; 24,14</t>
+          <t>14,53; 23,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,39; 21,0</t>
+          <t>13,97; 23,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>30,04; 55,8</t>
+          <t>30,97; 56,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,07; 41,49</t>
+          <t>20,79; 40,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,6; 58,31</t>
+          <t>30,47; 56,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>19,35; 40,42</t>
+          <t>24,82; 48,19</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,58</t>
+          <t>10,94</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>38,52%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 11,22</t>
+          <t>6,47; 11,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,61; 12,24</t>
+          <t>6,75; 12,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,42; 11,8</t>
+          <t>6,25; 11,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,61; 36,33</t>
+          <t>8,39; 13,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,79; 115,29</t>
+          <t>53,21; 114,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,43; 84,37</t>
+          <t>39,7; 84,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,05; 70,4</t>
+          <t>32,59; 69,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>44,65; 171,56</t>
+          <t>28,24; 52,54</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,2</t>
+          <t>9,78</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 12,24</t>
+          <t>2,37; 11,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 14,27</t>
+          <t>4,01; 13,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 7,35</t>
+          <t>-3,08; 7,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 14,91</t>
+          <t>5,35; 14,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,85; 127,36</t>
+          <t>17,31; 122,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,8; 162,56</t>
+          <t>28,42; 161,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 48,14</t>
+          <t>-14,61; 45,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,12; 61,67</t>
+          <t>18,09; 58,36</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,6</t>
+          <t>13,87</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,6; 15,67</t>
+          <t>11,49; 15,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,02; 16,69</t>
+          <t>11,97; 16,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,1; 14,79</t>
+          <t>10,09; 14,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,81; 29,52</t>
+          <t>11,71; 16,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,88; 83,27</t>
+          <t>55,13; 84,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,73; 71,53</t>
+          <t>47,16; 72,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,75; 65,65</t>
+          <t>40,14; 64,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,07; 116,31</t>
+          <t>33,98; 52,29</t>
         </is>
       </c>
     </row>
